--- a/STCI.xlsx
+++ b/STCI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaron\stci_lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE0B676-8F69-4FFA-A91E-73E072A44F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31204DFA-9A58-43DB-839F-D669C0291090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{53F45273-BCA5-4F10-9886-07DD9FC3A05C}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{53F45273-BCA5-4F10-9886-07DD9FC3A05C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Farenheit</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Alex</t>
+  </si>
+  <si>
+    <t>calculate_team_points</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,9 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
